--- a/data/00997A_20260826.xlsx
+++ b/data/00997A_20260826.xlsx
@@ -385,7 +385,7 @@
         <v>基金淨資產價值(元)</v>
       </c>
       <c r="B1" t="str">
-        <v>TWD 12,882,083,814</v>
+        <v>TWD 13,037,095,977</v>
       </c>
     </row>
     <row r="2">
@@ -393,7 +393,7 @@
         <v>每受益權單位淨資產價值(元)-台幣交易</v>
       </c>
       <c r="B2" t="str">
-        <v>TWD 10.97</v>
+        <v>TWD 11.12</v>
       </c>
     </row>
     <row r="3">
@@ -401,7 +401,7 @@
         <v>已發行受益權單位總數-台幣交易</v>
       </c>
       <c r="B3" t="str">
-        <v>1,173,877,000</v>
+        <v>1,171,877,000</v>
       </c>
     </row>
   </sheetData>
@@ -413,7 +413,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D53"/>
+  <dimension ref="A1:D52"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -437,7 +437,7 @@
         <v>美光科技公司</v>
       </c>
       <c r="C2" t="str">
-        <v>4.53%</v>
+        <v>4.59%</v>
       </c>
       <c r="D2" t="str">
         <v>20,095</v>
@@ -451,7 +451,7 @@
         <v>Marvell Technology Inc</v>
       </c>
       <c r="C3" t="str">
-        <v>4.38%</v>
+        <v>4.54%</v>
       </c>
       <c r="D3" t="str">
         <v>77,233</v>
@@ -465,7 +465,7 @@
         <v>ADVANCED MICRO DEVICES</v>
       </c>
       <c r="C4" t="str">
-        <v>3.7%</v>
+        <v>3.83%</v>
       </c>
       <c r="D4" t="str">
         <v>32,722</v>
@@ -473,44 +473,44 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>GOOGL US</v>
+        <v>LITE US</v>
       </c>
       <c r="B5" t="str">
-        <v>ALPHABET INC-CL A</v>
+        <v>魯門特姆控股公司</v>
       </c>
       <c r="C5" t="str">
-        <v>3.34%</v>
+        <v>3.36%</v>
       </c>
       <c r="D5" t="str">
-        <v>38,700</v>
+        <v>15,516</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>SNDK US</v>
+        <v>GOOGL US</v>
       </c>
       <c r="B6" t="str">
-        <v>晟碟公司（德拉瓦州）</v>
+        <v>ALPHABET INC-CL A</v>
       </c>
       <c r="C6" t="str">
-        <v>3.26%</v>
+        <v>3.28%</v>
       </c>
       <c r="D6" t="str">
-        <v>8,823</v>
+        <v>38,700</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>LITE US</v>
+        <v>SNDK US</v>
       </c>
       <c r="B7" t="str">
-        <v>魯門特姆控股公司</v>
+        <v>晟碟公司（德拉瓦州）</v>
       </c>
       <c r="C7" t="str">
-        <v>3.19%</v>
+        <v>3.2%</v>
       </c>
       <c r="D7" t="str">
-        <v>15,516</v>
+        <v>8,823</v>
       </c>
     </row>
     <row r="8">
@@ -521,7 +521,7 @@
         <v>應用材料</v>
       </c>
       <c r="C8" t="str">
-        <v>2.99%</v>
+        <v>2.93%</v>
       </c>
       <c r="D8" t="str">
         <v>24,965</v>
@@ -535,7 +535,7 @@
         <v>科林研發股份有限公司</v>
       </c>
       <c r="C9" t="str">
-        <v>2.83%</v>
+        <v>2.84%</v>
       </c>
       <c r="D9" t="str">
         <v>36,909</v>
@@ -549,7 +549,7 @@
         <v>揖斐電有限公司</v>
       </c>
       <c r="C10" t="str">
-        <v>2.65%</v>
+        <v>2.78%</v>
       </c>
       <c r="D10" t="str">
         <v>90,664</v>
@@ -563,7 +563,7 @@
         <v>輝達公司</v>
       </c>
       <c r="C11" t="str">
-        <v>2.64%</v>
+        <v>2.66%</v>
       </c>
       <c r="D11" t="str">
         <v>51,076</v>
@@ -571,58 +571,58 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>CRWD US</v>
+        <v>TER US</v>
       </c>
       <c r="B12" t="str">
-        <v>Crowdstrike控股公司</v>
+        <v>泰瑞達公司</v>
       </c>
       <c r="C12" t="str">
-        <v>2.63%</v>
+        <v>2.53%</v>
       </c>
       <c r="D12" t="str">
-        <v>55,605</v>
+        <v>28,213</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>TER US</v>
+        <v>CRWD US</v>
       </c>
       <c r="B13" t="str">
-        <v>泰瑞達公司</v>
+        <v>Crowdstrike控股公司</v>
       </c>
       <c r="C13" t="str">
-        <v>2.55%</v>
+        <v>2.52%</v>
       </c>
       <c r="D13" t="str">
-        <v>28,213</v>
+        <v>55,605</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>2330</v>
+        <v>STX US</v>
       </c>
       <c r="B14" t="str">
-        <v>台積電</v>
+        <v>希捷科技控股公開有限公司</v>
       </c>
       <c r="C14" t="str">
-        <v>2.43%</v>
+        <v>2.46%</v>
       </c>
       <c r="D14" t="str">
-        <v>132,000</v>
+        <v>12,253</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>STX US</v>
+        <v>2330</v>
       </c>
       <c r="B15" t="str">
-        <v>希捷科技控股公開有限公司</v>
+        <v>台積電</v>
       </c>
       <c r="C15" t="str">
-        <v>2.41%</v>
+        <v>2.43%</v>
       </c>
       <c r="D15" t="str">
-        <v>12,253</v>
+        <v>132,000</v>
       </c>
     </row>
     <row r="16">
@@ -633,7 +633,7 @@
         <v>蘋果公司</v>
       </c>
       <c r="C16" t="str">
-        <v>2.37%</v>
+        <v>2.34%</v>
       </c>
       <c r="D16" t="str">
         <v>30,890</v>
@@ -647,7 +647,7 @@
         <v>Howmet航太公司</v>
       </c>
       <c r="C17" t="str">
-        <v>2.35%</v>
+        <v>2.33%</v>
       </c>
       <c r="D17" t="str">
         <v>36,048</v>
@@ -655,58 +655,58 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>SNOW US</v>
+        <v>009150 KS</v>
       </c>
       <c r="B18" t="str">
-        <v>Snowflake公司</v>
+        <v>三星電機</v>
       </c>
       <c r="C18" t="str">
-        <v>2.24%</v>
+        <v>2.22%</v>
       </c>
       <c r="D18" t="str">
-        <v>27,997</v>
+        <v>9,224</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>PANW US</v>
+        <v>CRDO US</v>
       </c>
       <c r="B19" t="str">
-        <v>Palo Alto Networks Inc</v>
+        <v>Credo科技集團控股有限公司</v>
       </c>
       <c r="C19" t="str">
-        <v>2.23%</v>
+        <v>2.2%</v>
       </c>
       <c r="D19" t="str">
-        <v>25,679</v>
+        <v>39,735</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>CRDO US</v>
+        <v>SNOW US</v>
       </c>
       <c r="B20" t="str">
-        <v>Credo科技集團控股有限公司</v>
+        <v>Snowflake公司</v>
       </c>
       <c r="C20" t="str">
-        <v>2.19%</v>
+        <v>2.17%</v>
       </c>
       <c r="D20" t="str">
-        <v>39,735</v>
+        <v>27,997</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>009150 KS</v>
+        <v>PANW US</v>
       </c>
       <c r="B21" t="str">
-        <v>三星電機</v>
+        <v>Palo Alto Networks Inc</v>
       </c>
       <c r="C21" t="str">
-        <v>2.18%</v>
+        <v>2.13%</v>
       </c>
       <c r="D21" t="str">
-        <v>9,224</v>
+        <v>25,679</v>
       </c>
     </row>
     <row r="22">
@@ -717,7 +717,7 @@
         <v>Dynatrace公司</v>
       </c>
       <c r="C22" t="str">
-        <v>2.11%</v>
+        <v>2.13%</v>
       </c>
       <c r="D22" t="str">
         <v>174,101</v>
@@ -731,7 +731,7 @@
         <v>欣興</v>
       </c>
       <c r="C23" t="str">
-        <v>2%</v>
+        <v>2.02%</v>
       </c>
       <c r="D23" t="str">
         <v>240,000</v>
@@ -745,7 +745,7 @@
         <v>奇異公司</v>
       </c>
       <c r="C24" t="str">
-        <v>1.95%</v>
+        <v>1.97%</v>
       </c>
       <c r="D24" t="str">
         <v>22,986</v>
@@ -759,7 +759,7 @@
         <v>喜雅納公司</v>
       </c>
       <c r="C25" t="str">
-        <v>1.88%</v>
+        <v>1.93%</v>
       </c>
       <c r="D25" t="str">
         <v>20,397</v>
@@ -773,7 +773,7 @@
         <v>雷神科技公司</v>
       </c>
       <c r="C26" t="str">
-        <v>1.86%</v>
+        <v>1.85%</v>
       </c>
       <c r="D26" t="str">
         <v>35,894</v>
@@ -795,30 +795,30 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>AMZN US</v>
+        <v>2383</v>
       </c>
       <c r="B28" t="str">
-        <v>亞馬遜公司</v>
+        <v>台光電</v>
       </c>
       <c r="C28" t="str">
-        <v>1.77%</v>
+        <v>1.76%</v>
       </c>
       <c r="D28" t="str">
-        <v>27,274</v>
+        <v>41,000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>2383</v>
+        <v>AMZN US</v>
       </c>
       <c r="B29" t="str">
-        <v>台光電</v>
+        <v>亞馬遜公司</v>
       </c>
       <c r="C29" t="str">
-        <v>1.73%</v>
+        <v>1.74%</v>
       </c>
       <c r="D29" t="str">
-        <v>41,000</v>
+        <v>27,274</v>
       </c>
     </row>
     <row r="30">
@@ -837,128 +837,128 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>APH US</v>
+        <v>MRK US</v>
       </c>
       <c r="B31" t="str">
-        <v>安費諾</v>
+        <v>默克藥廠</v>
       </c>
       <c r="C31" t="str">
-        <v>1.39%</v>
+        <v>1.54%</v>
       </c>
       <c r="D31" t="str">
-        <v>36,017</v>
+        <v>40,144</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>INTC US</v>
+        <v>APH US</v>
       </c>
       <c r="B32" t="str">
-        <v>英特爾</v>
+        <v>安費諾</v>
       </c>
       <c r="C32" t="str">
-        <v>1.37%</v>
+        <v>1.4%</v>
       </c>
       <c r="D32" t="str">
-        <v>63,625</v>
+        <v>36,017</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>IOT US</v>
+        <v>INTC US</v>
       </c>
       <c r="B33" t="str">
-        <v>森萬聯有限公司</v>
+        <v>英特爾</v>
       </c>
       <c r="C33" t="str">
-        <v>1.34%</v>
+        <v>1.36%</v>
       </c>
       <c r="D33" t="str">
-        <v>133,951</v>
+        <v>63,625</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>AVGO US</v>
+        <v>IOT US</v>
       </c>
       <c r="B34" t="str">
-        <v>博通公司</v>
+        <v>森萬聯有限公司</v>
       </c>
       <c r="C34" t="str">
-        <v>1.24%</v>
+        <v>1.28%</v>
       </c>
       <c r="D34" t="str">
-        <v>13,926</v>
+        <v>133,951</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>PLTR US</v>
+        <v>AVGO US</v>
       </c>
       <c r="B35" t="str">
-        <v>帕蘭提爾科技公司</v>
+        <v>博通公司</v>
       </c>
       <c r="C35" t="str">
         <v>1.22%</v>
       </c>
       <c r="D35" t="str">
-        <v>27,930</v>
+        <v>13,926</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>OKTA US</v>
+        <v>PLTR US</v>
       </c>
       <c r="B36" t="str">
-        <v>Okta公司</v>
+        <v>帕蘭提爾科技公司</v>
       </c>
       <c r="C36" t="str">
-        <v>1.02%</v>
+        <v>1.18%</v>
       </c>
       <c r="D36" t="str">
-        <v>31,382</v>
+        <v>27,930</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>WDC US</v>
+        <v>OKTA US</v>
       </c>
       <c r="B37" t="str">
-        <v>WESTERN DIGITAL CORP</v>
+        <v>Okta公司</v>
       </c>
       <c r="C37" t="str">
-        <v>0.97%</v>
+        <v>1%</v>
       </c>
       <c r="D37" t="str">
-        <v>9,006</v>
+        <v>31,382</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>AXON US</v>
+        <v>WDC US</v>
       </c>
       <c r="B38" t="str">
-        <v>泰瑟國際公司</v>
+        <v>WESTERN DIGITAL CORP</v>
       </c>
       <c r="C38" t="str">
-        <v>0.96%</v>
+        <v>0.99%</v>
       </c>
       <c r="D38" t="str">
-        <v>6,500</v>
+        <v>9,006</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>2345</v>
+        <v>AXON US</v>
       </c>
       <c r="B39" t="str">
-        <v>智邦</v>
+        <v>泰瑟國際公司</v>
       </c>
       <c r="C39" t="str">
-        <v>0.9%</v>
+        <v>0.97%</v>
       </c>
       <c r="D39" t="str">
-        <v>56,000</v>
+        <v>6,500</v>
       </c>
     </row>
     <row r="40">
@@ -977,142 +977,142 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>MRK US</v>
+        <v>MSFT US</v>
       </c>
       <c r="B41" t="str">
-        <v>默克藥廠</v>
+        <v>微軟公司</v>
       </c>
       <c r="C41" t="str">
-        <v>0.81%</v>
+        <v>0.73%</v>
       </c>
       <c r="D41" t="str">
-        <v>21,700</v>
+        <v>6,083</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>285A JP</v>
+        <v>META US</v>
       </c>
       <c r="B42" t="str">
-        <v>鎧俠控股公司</v>
+        <v>Meta平台公司</v>
       </c>
       <c r="C42" t="str">
-        <v>0.74%</v>
+        <v>0.73%</v>
       </c>
       <c r="D42" t="str">
-        <v>9,282</v>
+        <v>5,236</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>MSFT US</v>
+        <v>285A JP</v>
       </c>
       <c r="B43" t="str">
-        <v>微軟公司</v>
+        <v>鎧俠控股公司</v>
       </c>
       <c r="C43" t="str">
-        <v>0.73%</v>
+        <v>0.72%</v>
       </c>
       <c r="D43" t="str">
-        <v>6,083</v>
+        <v>9,182</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>META US</v>
+        <v>KEYS US</v>
       </c>
       <c r="B44" t="str">
-        <v>Meta平台公司</v>
+        <v>是德科技公司</v>
       </c>
       <c r="C44" t="str">
-        <v>0.72%</v>
+        <v>0.64%</v>
       </c>
       <c r="D44" t="str">
-        <v>5,236</v>
+        <v>8,196</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>KEYS US</v>
+        <v>COHR US</v>
       </c>
       <c r="B45" t="str">
-        <v>是德科技公司</v>
+        <v>連貫公司</v>
       </c>
       <c r="C45" t="str">
-        <v>0.63%</v>
+        <v>0.64%</v>
       </c>
       <c r="D45" t="str">
-        <v>8,196</v>
+        <v>9,022</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>COHR US</v>
+        <v>MPWR US</v>
       </c>
       <c r="B46" t="str">
-        <v>連貫公司</v>
+        <v>芯源系統有限公司</v>
       </c>
       <c r="C46" t="str">
-        <v>0.62%</v>
+        <v>0.57%</v>
       </c>
       <c r="D46" t="str">
-        <v>9,022</v>
+        <v>1,799</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>MPWR US</v>
+        <v>ADBE US</v>
       </c>
       <c r="B47" t="str">
-        <v>芯源系統有限公司</v>
+        <v>奧多比系統公司</v>
       </c>
       <c r="C47" t="str">
-        <v>0.57%</v>
+        <v>0.55%</v>
       </c>
       <c r="D47" t="str">
-        <v>1,799</v>
+        <v>8,282</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>ADBE US</v>
+        <v>KLAC US</v>
       </c>
       <c r="B48" t="str">
-        <v>奧多比系統公司</v>
+        <v>KLA CORP</v>
       </c>
       <c r="C48" t="str">
-        <v>0.57%</v>
+        <v>0.5%</v>
       </c>
       <c r="D48" t="str">
-        <v>8,282</v>
+        <v>11,245</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>KLAC US</v>
+        <v>ALAB US</v>
       </c>
       <c r="B49" t="str">
-        <v>KLA CORP</v>
+        <v>Astera實驗室公司</v>
       </c>
       <c r="C49" t="str">
-        <v>0.51%</v>
+        <v>0.45%</v>
       </c>
       <c r="D49" t="str">
-        <v>11,245</v>
+        <v>6,551</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>ALAB US</v>
+        <v>CDNS US</v>
       </c>
       <c r="B50" t="str">
-        <v>Astera實驗室公司</v>
+        <v>Cadence設計系統公司</v>
       </c>
       <c r="C50" t="str">
-        <v>0.45%</v>
+        <v>0.32%</v>
       </c>
       <c r="D50" t="str">
-        <v>6,551</v>
+        <v>3,905</v>
       </c>
     </row>
     <row r="51">
@@ -1131,35 +1131,21 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>CDNS US</v>
+        <v>APP US</v>
       </c>
       <c r="B52" t="str">
-        <v>Cadence設計系統公司</v>
+        <v>AppLovin公司</v>
       </c>
       <c r="C52" t="str">
-        <v>0.31%</v>
+        <v>0.24%</v>
       </c>
       <c r="D52" t="str">
-        <v>3,905</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="str">
-        <v>APP US</v>
-      </c>
-      <c r="B53" t="str">
-        <v>AppLovin公司</v>
-      </c>
-      <c r="C53" t="str">
-        <v>0.23%</v>
-      </c>
-      <c r="D53" t="str">
         <v>3,145</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D53"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D52"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1181,7 +1167,7 @@
         <v>債券附買回-P13鴻海1B</v>
       </c>
       <c r="B2" t="str">
-        <v>TWD 40,014,708.00</v>
+        <v>TWD 40,025,215.00</v>
       </c>
     </row>
     <row r="3">
@@ -1189,7 +1175,7 @@
         <v>債券附買回-P13鴻海2B</v>
       </c>
       <c r="B3" t="str">
-        <v>TWD 40,000,000.00</v>
+        <v>TWD 40,008,581.00</v>
       </c>
     </row>
   </sheetData>
@@ -1201,43 +1187,59 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
         <v>應收付證券款</v>
       </c>
       <c r="B1" t="str">
-        <v>USD 6,596,376.27</v>
+        <v>JPY 5,069,385.00</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>應付贖回款</v>
+        <v>應收付證券款</v>
       </c>
       <c r="B2" t="str">
-        <v>TWD -482,859,259.00</v>
+        <v>TWD 111,008,011.00</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>現金</v>
+        <v>應收付證券款</v>
       </c>
       <c r="B3" t="str">
-        <v>TWD 331,575,624.00</v>
+        <v>USD -2,854,347.33</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
+        <v>應付贖回款</v>
+      </c>
+      <c r="B4" t="str">
+        <v>TWD -487,130,409.00</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
         <v>現金</v>
       </c>
-      <c r="B4" t="str">
-        <v>USD 26,458,784.95</v>
+      <c r="B5" t="str">
+        <v>TWD 313,616,082.00</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>現金</v>
+      </c>
+      <c r="B6" t="str">
+        <v>USD 33,058,814.46</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B6"/>
   </ignoredErrors>
 </worksheet>
 </file>